--- a/docs/BillOfMaterials.xlsx
+++ b/docs/BillOfMaterials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fredd\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\UJConnect\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8352D46-4CF9-4BF2-BBC2-F2630E1F403A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB88302A-1856-489F-9219-E64BFFF564C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,24 +68,12 @@
     <t>Source / URL</t>
   </si>
   <si>
-    <t>Database Hosting</t>
-  </si>
-  <si>
     <t>Infrastructure</t>
   </si>
   <si>
-    <t>Aiven</t>
-  </si>
-  <si>
-    <t>MySQL — Developer Tier</t>
-  </si>
-  <si>
     <t>months</t>
   </si>
   <si>
-    <t>aiven.io/pricing</t>
-  </si>
-  <si>
     <t>Web / App Hosting</t>
   </si>
   <si>
@@ -221,9 +209,6 @@
     <t>Assumes ~50GB Year-1 storage (product photos + tutor proof-of-mark documents)</t>
   </si>
   <si>
-    <t>Developer tier runs 24/7 on a dedicated VM with basic support</t>
-  </si>
-  <si>
     <t>Third-party estimates for B1 Linux ranged $13-55/mo depending on OS and source</t>
   </si>
   <si>
@@ -237,6 +222,21 @@
   </si>
   <si>
     <t>TOTAL ESTIMATED ONCE OFF COSTS</t>
+  </si>
+  <si>
+    <t>Raspberry pi</t>
+  </si>
+  <si>
+    <t>(Hardware) Infrastructure</t>
+  </si>
+  <si>
+    <t>COMMUNICA Electronics</t>
+  </si>
+  <si>
+    <t>https://www.communica.co.za/products/raspberry-pi-5b-8gb?variant=48701473980716&amp;sfdr_ptcid=31591_617_703365267&amp;sfdr_hash=6ae3baa44d2566514ab4895cab43a727&amp;utm_source=www.communica.co.za&amp;gad_source=1&amp;gad_campaignid=24042158071&amp;gbraid=0AAAAADLTnIaHDfYUxfjKqOBPUwcszsvNH&amp;gclid=Cj0KCQjwh4TVBhCWARIsAG0czmo9ZobSoXrddhBMC6kAy1PRiFD5e4js4bCJDJv26hXgXu3Zh9l6ok4aApwbEALw_wcB</t>
+  </si>
+  <si>
+    <t>Used to host our database</t>
   </si>
 </sst>
 </file>
@@ -715,7 +715,7 @@
     </row>
     <row r="2" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -756,40 +756,40 @@
         <v>9</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="6">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H5" s="6">
         <f t="shared" ref="H5:H14" si="0">E5*F5</f>
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>61</v>
+      <c r="J5" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -797,7 +797,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>17</v>
@@ -806,23 +806,23 @@
         <v>18</v>
       </c>
       <c r="E6" s="6">
-        <v>213</v>
+        <v>323</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H6" s="6">
         <f t="shared" si="0"/>
-        <v>213</v>
+        <v>323</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>62</v>
+      <c r="J6" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -830,244 +830,244 @@
         <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" s="6">
-        <v>323</v>
+        <v>15</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H7" s="6">
         <f t="shared" si="0"/>
-        <v>323</v>
+        <v>15</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>59</v>
+        <v>22</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E8" s="6">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H8" s="6">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f t="shared" ref="H8" si="1">E8*F8</f>
+        <v>1800</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E9" s="6">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="H9" s="6">
-        <f t="shared" ref="H9" si="1">E9*F9</f>
-        <v>1800</v>
-      </c>
-      <c r="I9" s="2" t="s">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>54</v>
+      <c r="J9" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>56</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E10" s="6">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>57</v>
+        <v>197</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="6">
-        <v>197</v>
+        <v>125</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H11" s="6">
         <f t="shared" si="0"/>
-        <v>197</v>
+        <v>125</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E12" s="6">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H12" s="6">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E13" s="6">
-        <v>50</v>
+        <v>4620</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H13" s="6">
-        <f t="shared" si="0"/>
-        <v>50</v>
+        <f t="shared" ref="H13" si="2">E13*F13</f>
+        <v>4620</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E14" s="6">
         <v>3000</v>
@@ -1076,23 +1076,23 @@
         <v>1</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H14" s="6">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:10" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -1101,13 +1101,13 @@
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
       <c r="H16" s="3">
-        <f>SUM(H12:H15)</f>
-        <v>3175</v>
+        <f>SUM(H9:H15)</f>
+        <v>7992</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -1116,8 +1116,8 @@
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="3">
-        <f>SUM(H5:H9)</f>
-        <v>2432</v>
+        <f>SUM(H5:H8)</f>
+        <v>2351</v>
       </c>
     </row>
   </sheetData>
@@ -1283,18 +1283,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1316,6 +1316,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BDAFE94-8959-41EA-9607-D603F185818E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA56F417-F145-4FD1-B001-1CB2146D83FC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -1329,12 +1337,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BDAFE94-8959-41EA-9607-D603F185818E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>